--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,22 +342,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,22 +846,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,166 +873,181 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1054,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1081,12 +1096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1108,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1135,12 +1150,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1162,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1189,12 +1204,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1204,7 +1219,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1216,12 +1231,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1243,12 +1258,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1270,12 +1285,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1285,7 +1300,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1297,12 +1312,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1324,12 +1339,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1351,12 +1366,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1378,12 +1393,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1405,12 +1420,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1432,12 +1447,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1459,12 +1474,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1486,12 +1501,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1513,12 +1528,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1540,12 +1555,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1555,7 +1570,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1567,12 +1582,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1594,83 +1609,110 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2731000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>325769.92</t>
+          <t>2901000</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>338608</t>
+          <t>345769.92</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>338608</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>-12838.08</t>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>7161.92</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1042,12 +1042,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1069,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1096,12 +1096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1123,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1150,12 +1150,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1177,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1204,12 +1204,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1231,12 +1231,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1258,12 +1258,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1285,12 +1285,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1312,12 +1312,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1420,12 +1420,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1474,12 +1474,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1528,12 +1528,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1555,12 +1555,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1582,12 +1582,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1636,83 +1636,110 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2901000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>345769.92</t>
+          <t>2901000</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>338608</t>
+          <t>345769.92</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>358608</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>7161.92</t>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-12838.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/15 10:26:14</t>
+          <t>09/17 10:03:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,22 +342,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,22 +804,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,22 +888,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,166 +915,181 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1096,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1123,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1150,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1177,12 +1192,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1204,12 +1219,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1231,12 +1246,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1258,12 +1273,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1273,7 +1288,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1285,12 +1300,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1312,12 +1327,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1339,12 +1354,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1354,7 +1369,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1366,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1393,12 +1408,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1420,12 +1435,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1447,12 +1462,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1474,12 +1489,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1501,12 +1516,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1528,12 +1543,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1555,12 +1570,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1582,12 +1597,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1609,12 +1624,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1624,7 +1639,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1636,12 +1651,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1663,83 +1678,110 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2901000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>345769.92</t>
+          <t>3001000</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>358608</t>
+          <t>357534.62</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>358608</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>-12838.08</t>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>-1073.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1084,12 +1084,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1111,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1138,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1192,12 +1192,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1219,12 +1219,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1246,12 +1246,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1273,12 +1273,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1300,12 +1300,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1354,12 +1354,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1408,12 +1408,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1462,12 +1462,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1489,12 +1489,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1516,12 +1516,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1543,12 +1543,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1570,12 +1570,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1597,12 +1597,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1624,12 +1624,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1651,12 +1651,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1678,12 +1678,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1705,83 +1705,110 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>3001000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>357534.62</t>
+          <t>3001000</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>358608</t>
+          <t>357534.62</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>358896</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>-1073.38</t>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>-1361.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1084,12 +1084,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1111,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1138,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1192,12 +1192,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1219,12 +1219,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1246,12 +1246,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1273,12 +1273,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1300,12 +1300,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1354,12 +1354,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1408,12 +1408,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1462,12 +1462,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1489,12 +1489,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1516,12 +1516,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1543,12 +1543,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1570,12 +1570,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1597,12 +1597,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1624,12 +1624,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1651,12 +1651,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1678,12 +1678,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1705,12 +1705,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1732,83 +1732,110 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>3001000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>357534.62</t>
+          <t>3001000</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>358896</t>
+          <t>357534.62</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>370372</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>-1361.38</t>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>-12837.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 10:03:28</t>
+          <t>09/23 15:27:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/15 10:26:14</t>
+          <t>09/17 10:03:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,22 +342,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,17 +725,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,17 +804,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,22 +846,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,22 +930,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,166 +957,181 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1126,7 +1141,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1138,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1153,7 +1168,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1165,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1192,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1219,12 +1234,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1246,12 +1261,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1273,12 +1288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1300,12 +1315,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1327,12 +1342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1354,12 +1369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1369,7 +1384,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1381,12 +1396,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1408,12 +1423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1435,12 +1450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1450,7 +1465,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1462,12 +1477,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1489,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1516,12 +1531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1543,12 +1558,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1570,12 +1585,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1597,12 +1612,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1624,12 +1639,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1651,12 +1666,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1678,12 +1693,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1705,12 +1720,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1720,7 +1735,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1732,12 +1747,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1759,83 +1774,110 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>3001000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>357534.62</t>
+          <t>3146000</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>370372</t>
+          <t>374796.53</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>370372</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>-12837.38</t>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>4424.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1126,12 +1126,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1153,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1180,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1207,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1234,12 +1234,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1261,12 +1261,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1288,12 +1288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1342,12 +1342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1369,12 +1369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1396,12 +1396,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1450,12 +1450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1477,12 +1477,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1504,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1612,12 +1612,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1639,12 +1639,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1666,12 +1666,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1693,12 +1693,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1720,12 +1720,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1747,12 +1747,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1801,83 +1801,110 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>3146000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>374796.53</t>
+          <t>3146000</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>370372</t>
+          <t>374796.53</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>370560</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>4424.53</t>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>4236.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1126,12 +1126,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1153,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1180,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1207,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1234,12 +1234,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1261,12 +1261,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1288,12 +1288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1342,12 +1342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1369,12 +1369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1396,12 +1396,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1450,12 +1450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1477,12 +1477,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1504,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1612,12 +1612,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1639,12 +1639,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1666,12 +1666,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1693,12 +1693,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1720,12 +1720,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1747,12 +1747,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1801,12 +1801,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1828,83 +1828,110 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>3146000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>374796.53</t>
+          <t>3146000</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>370560</t>
+          <t>374796.53</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>387633</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>4236.53</t>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>-12836.47</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23 15:27:39</t>
+          <t>09/24 10:57:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17 10:03:28</t>
+          <t>09/23 15:27:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/15 10:26:14</t>
+          <t>09/17 10:03:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,12 +179,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,17 +216,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,22 +342,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,22 +468,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,17 +678,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,22 +888,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,17 +935,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,22 +972,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,166 +999,181 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1180,12 +1195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1207,12 +1222,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1234,12 +1249,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1261,12 +1276,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1276,7 +1291,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1288,12 +1303,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1315,12 +1330,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1342,12 +1357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1369,12 +1384,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1396,12 +1411,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1423,7 +1438,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1450,12 +1465,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1465,7 +1480,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1477,12 +1492,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1492,7 +1507,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1504,12 +1519,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1531,12 +1546,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1546,7 +1561,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1558,12 +1573,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1573,7 +1588,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1585,12 +1600,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1612,12 +1627,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1639,12 +1654,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1666,12 +1681,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1693,12 +1708,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1720,12 +1735,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1747,12 +1762,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1774,12 +1789,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1801,12 +1816,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1816,7 +1831,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1828,12 +1843,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1843,7 +1858,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1855,12 +1870,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/07 12:28:03</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>58823</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1870,7 +1885,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1879,59 +1894,113 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>3146000</t>
-        </is>
-      </c>
-    </row>
+          <t>07/07 12:28:03</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>58823</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>374796.53</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>387633</t>
+          <t>3196000</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>380678.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>388021</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>-12836.47</t>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>-7342.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1168,12 +1168,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1222,12 +1222,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1249,12 +1249,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1276,12 +1276,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1357,12 +1357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1384,12 +1384,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1411,12 +1411,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1438,12 +1438,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1465,12 +1465,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1492,12 +1492,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1546,12 +1546,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1573,12 +1573,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1600,12 +1600,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1708,12 +1708,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1762,12 +1762,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1789,12 +1789,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1816,12 +1816,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1843,12 +1843,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1870,12 +1870,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1924,83 +1924,110 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>3196000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>380678.88</t>
+          <t>3196000</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>388021</t>
+          <t>380678.88</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>393515</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>-7342.12</t>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>-12836.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 10:57:00</t>
+          <t>09/29 20:58:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>18823.53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23 15:27:39</t>
+          <t>09/24 10:57:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/17 10:03:28</t>
+          <t>09/23 15:27:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/15 10:26:14</t>
+          <t>09/17 10:03:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,12 +221,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,22 +468,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,22 +510,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,22 +930,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,17 +977,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,22 +1014,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,166 +1041,181 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1222,12 +1237,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1237,7 +1252,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1249,12 +1264,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1264,7 +1279,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1276,12 +1291,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1291,7 +1306,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1303,12 +1318,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1318,7 +1333,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1330,12 +1345,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1345,7 +1360,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1357,12 +1372,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1384,12 +1399,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1411,12 +1426,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1438,12 +1453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1465,12 +1480,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1492,12 +1507,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1519,12 +1534,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1546,12 +1561,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1561,7 +1576,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1573,12 +1588,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1600,12 +1615,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1627,12 +1642,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1642,7 +1657,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1654,12 +1669,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1681,12 +1696,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1708,12 +1723,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1735,12 +1750,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1762,12 +1777,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1789,12 +1804,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1816,12 +1831,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1843,12 +1858,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1870,12 +1885,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1897,12 +1912,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1912,7 +1927,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1924,12 +1939,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1951,83 +1966,110 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>3196000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>380678.88</t>
+          <t>3356000</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>393515</t>
+          <t>399502.41</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>393515</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>-12836.12</t>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5987.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1210,12 +1210,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1264,12 +1264,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1318,12 +1318,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1345,12 +1345,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1372,12 +1372,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1399,12 +1399,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1426,12 +1426,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1453,12 +1453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1480,12 +1480,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1534,12 +1534,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1561,12 +1561,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1588,12 +1588,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1642,12 +1642,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1669,12 +1669,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1696,12 +1696,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1750,12 +1750,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1777,12 +1777,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1804,12 +1804,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1858,12 +1858,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1885,12 +1885,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1912,12 +1912,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1939,12 +1939,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -1966,12 +1966,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1993,83 +1993,110 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>3356000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>399502.41</t>
+          <t>3356000</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>393515</t>
+          <t>399502.41</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>393703</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>5987.41</t>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5799.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 20:58:34</t>
+          <t>10/01 14:45:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18823.53</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24 10:57:00</t>
+          <t>09/29 20:58:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>18823.53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23 15:27:39</t>
+          <t>09/24 10:57:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/17 10:03:28</t>
+          <t>09/23 15:27:39</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/15 10:26:14</t>
+          <t>09/17 10:03:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,12 +263,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,17 +300,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,22 +468,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,22 +510,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,17 +930,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,22 +972,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,22 +1056,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,166 +1083,181 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/29 21:09:02</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1252,7 +1267,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1264,12 +1279,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1291,12 +1306,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1306,7 +1321,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1318,12 +1333,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1333,7 +1348,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1345,12 +1360,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1360,7 +1375,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1372,12 +1387,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1387,7 +1402,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1399,12 +1414,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1414,7 +1429,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1426,12 +1441,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1453,12 +1468,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1480,12 +1495,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1507,12 +1522,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1534,12 +1549,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1561,12 +1576,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1588,12 +1603,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1615,12 +1630,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1630,7 +1645,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1642,12 +1657,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1669,12 +1684,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1696,12 +1711,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1711,7 +1726,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1723,12 +1738,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1750,12 +1765,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1777,12 +1792,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1804,12 +1819,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1831,12 +1846,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1858,12 +1873,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1885,12 +1900,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1912,12 +1927,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1939,12 +1954,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1966,12 +1981,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1981,7 +1996,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -1993,12 +2008,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2020,83 +2035,110 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>3356000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>399502.41</t>
+          <t>3456000</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>393703</t>
+          <t>411550.6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>393703</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>5799.41</t>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>17847.6</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1252,12 +1252,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/29 21:09:02</t>
+          <t>10/01 15:51:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1279,12 +1279,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1306,12 +1306,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1333,12 +1333,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1360,12 +1360,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1414,12 +1414,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1441,12 +1441,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1468,12 +1468,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1495,12 +1495,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1522,12 +1522,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1549,12 +1549,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1576,12 +1576,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1603,12 +1603,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1630,12 +1630,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1684,12 +1684,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1711,12 +1711,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1792,12 +1792,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1819,12 +1819,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1846,12 +1846,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1900,12 +1900,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1927,12 +1927,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1981,12 +1981,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2008,12 +2008,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2035,12 +2035,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2062,83 +2062,110 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>3456000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>411550.6</t>
+          <t>3456000</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>393703</t>
+          <t>411550.6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>405751</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>17847.6</t>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5799.6</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/01 14:45:35</t>
+          <t>10/11 10:01:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/29 20:58:34</t>
+          <t>10/01 14:45:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18823.53</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24 10:57:00</t>
+          <t>09/29 20:58:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>18823.53</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23 15:27:39</t>
+          <t>09/24 10:57:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/17 10:03:28</t>
+          <t>09/23 15:27:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/15 10:26:14</t>
+          <t>09/17 10:03:28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,22 +468,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,22 +510,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,17 +804,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,22 +1014,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,166 +1125,181 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/01 15:51:12</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/29 21:09:02</t>
+          <t>10/11 10:01:38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1294,7 +1309,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1306,12 +1321,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>10/01 15:51:12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1333,12 +1348,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1348,7 +1363,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1360,12 +1375,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1375,7 +1390,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1387,12 +1402,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1414,12 +1429,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1441,12 +1456,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1468,12 +1483,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1495,12 +1510,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1510,7 +1525,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1522,12 +1537,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1549,12 +1564,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1576,12 +1591,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1603,12 +1618,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1630,12 +1645,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1657,7 +1672,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1684,12 +1699,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1699,7 +1714,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1711,12 +1726,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1726,7 +1741,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1738,12 +1753,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1765,12 +1780,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1780,7 +1795,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1792,12 +1807,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1807,7 +1822,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1819,12 +1834,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1846,12 +1861,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1873,12 +1888,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1900,12 +1915,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1927,12 +1942,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1954,12 +1969,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1981,12 +1996,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2008,12 +2023,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2035,12 +2050,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2050,7 +2065,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2062,12 +2077,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2077,7 +2092,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2089,12 +2104,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/07 12:28:03</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>58823</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2104,7 +2119,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2113,59 +2128,113 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>3456000</t>
-        </is>
-      </c>
-    </row>
+          <t>07/07 12:28:03</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>58823</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>411550.6</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>405751</t>
+          <t>3506000</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>417432.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>406039</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>5799.6</t>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>11393.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1294,12 +1294,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/11 10:01:38</t>
+          <t>10/11 13:28:54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1321,12 +1321,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/01 15:51:12</t>
+          <t>10/11 10:01:38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1348,12 +1348,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/29 21:09:02</t>
+          <t>10/01 15:51:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1375,12 +1375,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1402,12 +1402,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1429,12 +1429,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1456,12 +1456,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1510,12 +1510,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1537,12 +1537,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1564,12 +1564,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1618,12 +1618,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1645,12 +1645,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1672,12 +1672,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1726,12 +1726,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1753,12 +1753,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1780,12 +1780,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1807,12 +1807,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1834,12 +1834,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1861,12 +1861,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1888,12 +1888,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1915,12 +1915,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1942,12 +1942,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1969,12 +1969,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1996,12 +1996,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2023,12 +2023,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2050,12 +2050,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2077,12 +2077,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2104,12 +2104,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2131,12 +2131,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2158,83 +2158,110 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>3506000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>417432.96</t>
+          <t>3506000</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>406039</t>
+          <t>417432.96</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>411633</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>11393.96</t>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5799.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/11 10:01:32</t>
+          <t>10/13 12:17:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/01 14:45:35</t>
+          <t>10/11 10:01:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/29 20:58:34</t>
+          <t>10/01 14:45:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18823.53</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24 10:57:00</t>
+          <t>09/29 20:58:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>18823.53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23 15:27:39</t>
+          <t>09/24 10:57:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/17 10:03:28</t>
+          <t>09/23 15:27:39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/15 10:26:14</t>
+          <t>09/17 10:03:28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,12 +347,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,17 +384,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,22 +510,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,22 +636,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,17 +935,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,22 +1056,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,17 +1103,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,166 +1167,181 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/11 13:28:54</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/11 10:01:38</t>
+          <t>10/11 13:28:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1336,7 +1351,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1348,12 +1363,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/01 15:51:12</t>
+          <t>10/11 10:01:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1375,12 +1390,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/29 21:09:02</t>
+          <t>10/01 15:51:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1390,7 +1405,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1402,12 +1417,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1417,7 +1432,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1429,12 +1444,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1456,12 +1471,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1471,7 +1486,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1483,12 +1498,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1498,7 +1513,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1510,12 +1525,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1525,7 +1540,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1537,12 +1552,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1552,7 +1567,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1564,12 +1579,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1579,7 +1594,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1591,12 +1606,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1618,12 +1633,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1645,12 +1660,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1672,12 +1687,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1699,12 +1714,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1726,12 +1741,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1753,12 +1768,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1780,12 +1795,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1795,7 +1810,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1807,12 +1822,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1834,12 +1849,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1861,12 +1876,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1876,7 +1891,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1888,12 +1903,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1915,12 +1930,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1942,12 +1957,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1969,12 +1984,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1996,12 +2011,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2023,12 +2038,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2050,12 +2065,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2077,12 +2092,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2104,12 +2119,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2131,12 +2146,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2146,7 +2161,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2158,12 +2173,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2185,83 +2200,110 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>3506000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>417432.96</t>
+          <t>3606000</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>411633</t>
+          <t>429337.72</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>411633</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>5799.96</t>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>17704.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1336,12 +1336,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/11 13:28:54</t>
+          <t>10/13 13:53:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1363,12 +1363,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/11 10:01:38</t>
+          <t>10/11 13:28:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1390,12 +1390,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/01 15:51:12</t>
+          <t>10/11 10:01:38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1417,12 +1417,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/29 21:09:02</t>
+          <t>10/01 15:51:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1444,12 +1444,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1471,12 +1471,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1498,12 +1498,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1552,12 +1552,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1606,12 +1606,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1660,12 +1660,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1687,12 +1687,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1741,12 +1741,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1768,12 +1768,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1795,12 +1795,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1822,12 +1822,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1849,12 +1849,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1876,12 +1876,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1930,12 +1930,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1957,12 +1957,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1984,12 +1984,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2011,12 +2011,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2038,12 +2038,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2065,12 +2065,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2119,12 +2119,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2146,12 +2146,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2173,12 +2173,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2200,12 +2200,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2227,83 +2227,110 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="73"/>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>3606000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>429337.72</t>
+          <t>3606000</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>411633</t>
+          <t>429337.72</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>423537</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>17704.72</t>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5800.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/13 12:17:55</t>
+          <t>10/16 13:26:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>17365.27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/11 10:01:32</t>
+          <t>10/13 12:17:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/01 14:45:35</t>
+          <t>10/11 10:01:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/29 20:58:34</t>
+          <t>10/01 14:45:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18823.53</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24 10:57:00</t>
+          <t>09/29 20:58:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>18823.53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23 15:27:39</t>
+          <t>09/24 10:57:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/17 10:03:28</t>
+          <t>09/23 15:27:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/15 10:26:14</t>
+          <t>09/17 10:03:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,12 +389,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,17 +426,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,22 +636,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,22 +678,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,17 +977,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,166 +1209,181 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/13 13:53:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/11 13:28:54</t>
+          <t>10/13 13:53:32</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1390,12 +1405,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/11 10:01:38</t>
+          <t>10/11 13:28:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1405,7 +1420,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1417,12 +1432,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/01 15:51:12</t>
+          <t>10/11 10:01:38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1444,12 +1459,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/29 21:09:02</t>
+          <t>10/01 15:51:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1459,7 +1474,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1471,12 +1486,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1486,7 +1501,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1498,12 +1513,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1525,12 +1540,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1540,7 +1555,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1552,12 +1567,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1567,7 +1582,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1579,12 +1594,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1594,7 +1609,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1606,12 +1621,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1621,7 +1636,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1633,12 +1648,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1648,7 +1663,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1660,12 +1675,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1687,12 +1702,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1714,12 +1729,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1741,12 +1756,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1768,12 +1783,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1795,12 +1810,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1822,12 +1837,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1849,12 +1864,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1864,7 +1879,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1876,12 +1891,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1903,12 +1918,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1930,12 +1945,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1945,7 +1960,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1957,12 +1972,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1984,12 +1999,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2011,12 +2026,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2038,12 +2053,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2065,12 +2080,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2092,12 +2107,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2119,12 +2134,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2146,12 +2161,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2173,12 +2188,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2200,12 +2215,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2215,7 +2230,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2227,12 +2242,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2254,83 +2269,110 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>3606000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>429337.72</t>
+          <t>3751000</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>423537</t>
+          <t>446702.99</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>423537</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>5800.72</t>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>23165.99</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1378,12 +1378,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/13 13:53:32</t>
+          <t>10/16 15:30:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1405,12 +1405,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/11 13:28:54</t>
+          <t>10/13 13:53:32</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/11 10:01:38</t>
+          <t>10/11 13:28:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/01 15:51:12</t>
+          <t>10/11 10:01:38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1486,12 +1486,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/29 21:09:02</t>
+          <t>10/01 15:51:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1513,12 +1513,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1540,12 +1540,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1594,12 +1594,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1621,12 +1621,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1648,12 +1648,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1702,12 +1702,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1729,12 +1729,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1756,12 +1756,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1783,12 +1783,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1810,12 +1810,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1837,12 +1837,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1864,12 +1864,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1891,12 +1891,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1918,12 +1918,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1972,12 +1972,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1999,12 +1999,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2026,12 +2026,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2053,12 +2053,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2080,12 +2080,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2107,12 +2107,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2134,12 +2134,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2188,12 +2188,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2215,12 +2215,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2242,12 +2242,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2269,12 +2269,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2296,83 +2296,110 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>3751000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>446702.99</t>
+          <t>3751000</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>423537</t>
+          <t>446702.99</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>440902</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>23165.99</t>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5800.99</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/16 13:26:03</t>
+          <t>10/26 10:21:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17365.27</t>
+          <t>26506.02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/13 12:17:55</t>
+          <t>10/16 13:26:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>17365.27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/11 10:01:32</t>
+          <t>10/13 12:17:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/01 14:45:35</t>
+          <t>10/11 10:01:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/29 20:58:34</t>
+          <t>10/01 14:45:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18823.53</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24 10:57:00</t>
+          <t>09/29 20:58:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>18823.53</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23 15:27:39</t>
+          <t>09/24 10:57:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17 10:03:28</t>
+          <t>09/23 15:27:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/15 10:26:14</t>
+          <t>09/17 10:03:28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,12 +431,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,22 +636,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,22 +678,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,22 +720,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,17 +930,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,17 +1098,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,17 +1187,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,22 +1224,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,166 +1251,181 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/16 15:30:26</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/13 13:53:32</t>
+          <t>10/26 11:45:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1432,12 +1447,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/11 13:28:54</t>
+          <t>10/16 15:30:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1447,7 +1462,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1459,12 +1474,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/11 10:01:38</t>
+          <t>10/13 13:53:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1474,7 +1489,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1486,12 +1501,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/01 15:51:12</t>
+          <t>10/11 13:28:54</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1501,7 +1516,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1513,12 +1528,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/29 21:09:02</t>
+          <t>10/11 10:01:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1528,7 +1543,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1540,12 +1555,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>10/01 15:51:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1567,12 +1582,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1582,7 +1597,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1594,12 +1609,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1609,7 +1624,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1621,12 +1636,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1648,12 +1663,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1675,12 +1690,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1702,12 +1717,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1729,12 +1744,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1744,7 +1759,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1756,12 +1771,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1783,12 +1798,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1810,12 +1825,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1837,12 +1852,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1864,12 +1879,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1891,7 +1906,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1918,12 +1933,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1933,7 +1948,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1945,12 +1960,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1960,7 +1975,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1972,12 +1987,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1999,12 +2014,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2014,7 +2029,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2026,12 +2041,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2041,7 +2056,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2053,12 +2068,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2080,12 +2095,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2107,12 +2122,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2134,12 +2149,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2161,12 +2176,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2188,12 +2203,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2215,12 +2230,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2242,12 +2257,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2269,12 +2284,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2284,7 +2299,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2296,12 +2311,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2311,7 +2326,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2323,12 +2338,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/07 12:28:03</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>58823</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2338,7 +2353,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2347,59 +2362,113 @@
         </is>
       </c>
     </row>
-    <row r="76"/>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>3751000</t>
-        </is>
-      </c>
-    </row>
+          <t>07/07 12:28:03</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>58823</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>446702.99</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>440902</t>
+          <t>3971000</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>473209.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>467408</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>5800.99</t>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5801.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 10:21:47</t>
+          <t>10/30 20:12:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26506.02</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/16 13:26:03</t>
+          <t>10/26 10:21:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17365.27</t>
+          <t>26506.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/13 12:17:55</t>
+          <t>10/16 13:26:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>17365.27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/11 10:01:32</t>
+          <t>10/13 12:17:55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/01 14:45:35</t>
+          <t>10/11 10:01:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/29 20:58:34</t>
+          <t>10/01 14:45:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18823.53</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24 10:57:00</t>
+          <t>09/29 20:58:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>18823.53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23 15:27:39</t>
+          <t>09/24 10:57:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17 10:03:28</t>
+          <t>09/23 15:27:39</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/15 10:26:14</t>
+          <t>09/17 10:03:28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,22 +636,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/03 12:12:00</t>
+          <t>09/03 14:05:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,22 +678,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t>贾凌</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,22 +720,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/23 09:56:14</t>
+          <t>08/26 15:30:53</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>31666.67</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>马书文</t>
+          <t/>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,17 +1140,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/27 11:23:18</t>
+          <t>07/27 15:17:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>215000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>10714.29</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,17 +1229,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,166 +1293,181 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>07/15 13:16:56</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>10588.24</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>邓迎春</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>07/07 10:57:55</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>58823.53</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>张黎</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/26 11:45:40</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>26506</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/16 15:30:26</t>
+          <t>10/26 11:45:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1462,7 +1477,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1474,12 +1489,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/13 13:53:32</t>
+          <t>10/16 15:30:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1489,7 +1504,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1501,12 +1516,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/11 13:28:54</t>
+          <t>10/13 13:53:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1528,12 +1543,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/11 10:01:38</t>
+          <t>10/11 13:28:54</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1543,7 +1558,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1555,12 +1570,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/01 15:51:12</t>
+          <t>10/11 10:01:38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1582,12 +1597,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/29 21:09:02</t>
+          <t>10/01 15:51:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1597,7 +1612,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1609,12 +1624,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1624,7 +1639,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1636,12 +1651,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1663,12 +1678,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1678,7 +1693,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1690,12 +1705,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1705,7 +1720,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1717,12 +1732,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1732,7 +1747,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1744,12 +1759,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1759,7 +1774,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1771,12 +1786,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1786,7 +1801,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1798,12 +1813,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1825,12 +1840,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1852,12 +1867,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1879,12 +1894,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1906,12 +1921,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1933,12 +1948,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1960,12 +1975,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1987,12 +2002,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2002,7 +2017,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2014,12 +2029,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2041,12 +2056,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2068,12 +2083,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2083,7 +2098,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2095,12 +2110,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2122,12 +2137,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2149,12 +2164,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2176,12 +2191,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2203,12 +2218,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2230,12 +2245,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2257,12 +2272,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2284,12 +2299,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2311,12 +2326,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2338,12 +2353,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2353,7 +2368,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2365,12 +2380,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2392,83 +2407,110 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>3971000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>473209.01</t>
+          <t>4081000</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>467408</t>
+          <t>486304.25</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>467408</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>5801.01</t>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>18896.25</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-all.xlsx
@@ -1462,12 +1462,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/26 11:45:40</t>
+          <t>10/30 21:49:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>26506</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1489,12 +1489,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/16 15:30:26</t>
+          <t>10/26 11:45:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1516,12 +1516,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10/13 13:53:32</t>
+          <t>10/16 15:30:26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1543,12 +1543,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10/11 13:28:54</t>
+          <t>10/13 13:53:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1570,12 +1570,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/11 10:01:38</t>
+          <t>10/11 13:28:54</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1597,12 +1597,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10/01 15:51:12</t>
+          <t>10/11 10:01:38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1624,12 +1624,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/29 21:09:02</t>
+          <t>10/01 15:51:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1651,12 +1651,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/24 12:28:36</t>
+          <t>09/29 21:09:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1678,12 +1678,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
+          <t>09/24 12:28:36</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1705,12 +1705,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1732,12 +1732,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/23 15:27:50</t>
+          <t>09/23 17:00:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/17 11:34:30</t>
+          <t>09/23 15:27:50</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1786,12 +1786,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
+          <t>09/17 11:34:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1813,12 +1813,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/15 11:36:58</t>
+          <t>09/17 10:03:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1840,12 +1840,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/08 15:08:10</t>
+          <t>09/15 11:36:58</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/05 18:36:53</t>
+          <t>09/08 15:08:10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1894,12 +1894,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/04 18:27:05</t>
+          <t>09/05 18:36:53</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1921,12 +1921,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
+          <t>09/04 18:27:05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1948,12 +1948,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>09/03 15:50:47</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1975,12 +1975,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/02 17:19:29</t>
+          <t>09/03 14:06:24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2002,12 +2002,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
+          <t>09/02 17:19:29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2029,12 +2029,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/30 12:44:48</t>
+          <t>09/02 16:53:50</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2056,12 +2056,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/28 14:02:52</t>
+          <t>08/30 12:44:48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2083,12 +2083,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
+          <t>08/28 14:02:52</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2110,12 +2110,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/27 18:05:14</t>
+          <t>08/28 11:17:38</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2137,12 +2137,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/26 17:20:36</t>
+          <t>08/27 18:05:14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2164,12 +2164,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08/23 11:10:42</t>
+          <t>08/26 17:20:36</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2191,12 +2191,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08/12 15:50:44</t>
+          <t>08/23 11:10:42</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2218,12 +2218,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08/11 15:41:53</t>
+          <t>08/12 15:50:44</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2245,12 +2245,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08/07 15:15:17</t>
+          <t>08/11 15:41:53</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2272,12 +2272,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08/04 15:01:41</t>
+          <t>08/07 15:15:17</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2299,12 +2299,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08/04 15:01:25</t>
+          <t>08/04 15:01:41</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2326,12 +2326,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
+          <t>08/04 15:01:25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2353,12 +2353,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>07/27 16:38:35</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2380,12 +2380,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/24 12:13:55</t>
+          <t>07/27 12:29:51</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2407,12 +2407,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/15 14:22:07</t>
+          <t>07/24 12:13:55</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2434,83 +2434,110 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>07/07 12:28:03</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>58823</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>4081000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>486304.25</t>
+          <t>4081000</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>467408</t>
+          <t>486304.25</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>480503</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>18896.25</t>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5801.25</t>
         </is>
       </c>
     </row>
